--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964678</v>
+        <v>123964523</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471871</v>
+        <v>471894</v>
       </c>
       <c r="R2" t="n">
-        <v>7076764</v>
+        <v>7076712</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -959,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123964386</v>
+        <v>123964031</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,42 +970,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471865</v>
+        <v>471868</v>
       </c>
       <c r="R4" t="n">
-        <v>7076746</v>
+        <v>7076872</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1039,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,7 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,22 +1063,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123963577</v>
+        <v>123964781</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,21 +1112,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1141,13 +1136,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471727</v>
+        <v>471855</v>
       </c>
       <c r="R5" t="n">
-        <v>7077044</v>
+        <v>7076803</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,7 +1181,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,22 +1205,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123963664</v>
+        <v>123963743</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,37 +1254,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471738</v>
+        <v>471788</v>
       </c>
       <c r="R6" t="n">
-        <v>7077025</v>
+        <v>7076975</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1318,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1323,12 +1328,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,22 +1352,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1380,7 +1385,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123964523</v>
+        <v>123964678</v>
       </c>
       <c r="B7" t="n">
         <v>78788</v>
@@ -1420,13 +1425,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471894</v>
+        <v>471871</v>
       </c>
       <c r="R7" t="n">
-        <v>7076712</v>
+        <v>7076764</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1455,7 +1460,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1465,7 +1470,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1517,7 +1527,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123963803</v>
+        <v>123963841</v>
       </c>
       <c r="B8" t="n">
         <v>79870</v>
@@ -1562,13 +1572,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471859</v>
+        <v>471864</v>
       </c>
       <c r="R8" t="n">
-        <v>7076971</v>
+        <v>7076925</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1607,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,7 +1617,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1801,7 +1811,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123964781</v>
+        <v>123964386</v>
       </c>
       <c r="B10" t="n">
         <v>79869</v>
@@ -1835,19 +1845,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471855</v>
+        <v>471865</v>
       </c>
       <c r="R10" t="n">
-        <v>7076803</v>
+        <v>7076746</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1876,7 +1891,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1886,12 +1901,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1943,7 +1953,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123964621</v>
+        <v>123964646</v>
       </c>
       <c r="B11" t="n">
         <v>79870</v>
@@ -1977,24 +1987,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471910</v>
+        <v>471902</v>
       </c>
       <c r="R11" t="n">
-        <v>7076731</v>
+        <v>7076746</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2023,7 +2028,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2033,7 +2038,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2062,12 +2067,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2227,10 +2232,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123964646</v>
+        <v>123963577</v>
       </c>
       <c r="B13" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2243,21 +2248,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2267,13 +2272,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471902</v>
+        <v>471727</v>
       </c>
       <c r="R13" t="n">
-        <v>7076746</v>
+        <v>7077044</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2302,7 +2307,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2312,7 +2317,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2331,22 +2336,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2364,10 +2369,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123963892</v>
+        <v>123964621</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2380,37 +2385,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471865</v>
+        <v>471910</v>
       </c>
       <c r="R14" t="n">
-        <v>7076927</v>
+        <v>7076731</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2439,7 +2449,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2449,12 +2459,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2473,22 +2478,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2506,7 +2511,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123964031</v>
+        <v>123963892</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2546,13 +2551,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471868</v>
+        <v>471865</v>
       </c>
       <c r="R15" t="n">
-        <v>7076872</v>
+        <v>7076927</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2581,7 +2586,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2591,12 +2596,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2648,7 +2653,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123963841</v>
+        <v>123963803</v>
       </c>
       <c r="B16" t="n">
         <v>79870</v>
@@ -2693,13 +2698,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471864</v>
+        <v>471859</v>
       </c>
       <c r="R16" t="n">
-        <v>7076925</v>
+        <v>7076971</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2728,7 +2733,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2738,7 +2743,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2790,10 +2795,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123964115</v>
+        <v>123963664</v>
       </c>
       <c r="B17" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2806,42 +2811,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471850</v>
+        <v>471738</v>
       </c>
       <c r="R17" t="n">
-        <v>7076819</v>
+        <v>7077025</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2880,7 +2880,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2899,22 +2904,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2932,7 +2937,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123963743</v>
+        <v>123964115</v>
       </c>
       <c r="B18" t="n">
         <v>79870</v>
@@ -2977,13 +2982,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471788</v>
+        <v>471850</v>
       </c>
       <c r="R18" t="n">
-        <v>7076975</v>
+        <v>7076819</v>
       </c>
       <c r="S18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3012,7 +3017,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3022,12 +3027,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3077,6 +3077,541 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124025507</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>472052</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7076789</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124025506</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>472001</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7076620</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124025516</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>471711</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7077040</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124025510</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>471995</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7076863</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Hack färska</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124025505</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57491</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norra Skärvången NÖ, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>471942</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7076805</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964523</v>
+        <v>123963577</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471894</v>
+        <v>471727</v>
       </c>
       <c r="R2" t="n">
-        <v>7076712</v>
+        <v>7077044</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123963999</v>
+        <v>123964115</v>
       </c>
       <c r="B3" t="n">
         <v>79870</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471870</v>
+        <v>471850</v>
       </c>
       <c r="R3" t="n">
-        <v>7076894</v>
+        <v>7076819</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,7 +954,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123964031</v>
+        <v>123964523</v>
       </c>
       <c r="B4" t="n">
         <v>78788</v>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471868</v>
+        <v>471894</v>
       </c>
       <c r="R4" t="n">
-        <v>7076872</v>
+        <v>7076712</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1096,10 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123964781</v>
+        <v>123964678</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,21 +1107,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1136,13 +1131,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471855</v>
+        <v>471871</v>
       </c>
       <c r="R5" t="n">
-        <v>7076803</v>
+        <v>7076764</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1171,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,12 +1176,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,22 +1200,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1238,10 +1233,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123963743</v>
+        <v>123964031</v>
       </c>
       <c r="B6" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,42 +1249,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471788</v>
+        <v>471868</v>
       </c>
       <c r="R6" t="n">
-        <v>7076975</v>
+        <v>7076872</v>
       </c>
       <c r="S6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1318,7 +1308,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1328,12 +1318,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,22 +1342,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1385,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123964678</v>
+        <v>123963999</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1401,34 +1391,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471871</v>
+        <v>471870</v>
       </c>
       <c r="R7" t="n">
-        <v>7076764</v>
+        <v>7076894</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1460,7 +1455,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1470,12 +1465,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,22 +1484,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123963841</v>
+        <v>123963664</v>
       </c>
       <c r="B8" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1543,39 +1533,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471864</v>
+        <v>471738</v>
       </c>
       <c r="R8" t="n">
-        <v>7076925</v>
+        <v>7077025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1607,7 +1592,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1617,7 +1602,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1636,22 +1626,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1669,7 +1659,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123963518</v>
+        <v>123963803</v>
       </c>
       <c r="B9" t="n">
         <v>79870</v>
@@ -1714,13 +1704,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471708</v>
+        <v>471859</v>
       </c>
       <c r="R9" t="n">
-        <v>7077042</v>
+        <v>7076971</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1749,7 +1739,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1759,7 +1749,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1811,10 +1801,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123964386</v>
+        <v>123963743</v>
       </c>
       <c r="B10" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1827,21 +1817,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1856,13 +1846,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471865</v>
+        <v>471788</v>
       </c>
       <c r="R10" t="n">
-        <v>7076746</v>
+        <v>7076975</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1891,7 +1881,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1901,7 +1891,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1953,7 +1948,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123964646</v>
+        <v>123963518</v>
       </c>
       <c r="B11" t="n">
         <v>79870</v>
@@ -1987,19 +1982,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471902</v>
+        <v>471708</v>
       </c>
       <c r="R11" t="n">
-        <v>7076746</v>
+        <v>7077042</v>
       </c>
       <c r="S11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2090,7 +2090,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123964409</v>
+        <v>123963841</v>
       </c>
       <c r="B12" t="n">
         <v>79870</v>
@@ -2135,13 +2135,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471878</v>
+        <v>471864</v>
       </c>
       <c r="R12" t="n">
-        <v>7076764</v>
+        <v>7076925</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123963577</v>
+        <v>123963892</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471727</v>
+        <v>471865</v>
       </c>
       <c r="R13" t="n">
-        <v>7077044</v>
+        <v>7076927</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2317,7 +2317,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2369,7 +2374,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123964621</v>
+        <v>123964409</v>
       </c>
       <c r="B14" t="n">
         <v>79870</v>
@@ -2414,13 +2419,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471910</v>
+        <v>471878</v>
       </c>
       <c r="R14" t="n">
-        <v>7076731</v>
+        <v>7076764</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2449,7 +2454,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2459,7 +2464,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2511,10 +2516,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123963892</v>
+        <v>123964386</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2527,24 +2532,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
@@ -2554,10 +2564,10 @@
         <v>471865</v>
       </c>
       <c r="R15" t="n">
-        <v>7076927</v>
+        <v>7076746</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2586,7 +2596,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2596,12 +2606,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2620,22 +2625,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123963803</v>
+        <v>123964781</v>
       </c>
       <c r="B16" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2669,42 +2674,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471859</v>
+        <v>471855</v>
       </c>
       <c r="R16" t="n">
-        <v>7076971</v>
+        <v>7076803</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2743,7 +2743,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2795,10 +2800,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123963664</v>
+        <v>123964646</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2811,21 +2816,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2835,13 +2840,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471738</v>
+        <v>471902</v>
       </c>
       <c r="R17" t="n">
-        <v>7077025</v>
+        <v>7076746</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2870,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2880,12 +2885,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2904,22 +2904,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123964115</v>
+        <v>123964621</v>
       </c>
       <c r="B18" t="n">
         <v>79870</v>
@@ -2982,10 +2982,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471850</v>
+        <v>471910</v>
       </c>
       <c r="R18" t="n">
-        <v>7076819</v>
+        <v>7076731</v>
       </c>
       <c r="S18" t="n">
         <v>9</v>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025506</v>
+        <v>124025510</v>
       </c>
       <c r="B20" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472001</v>
+        <v>471995</v>
       </c>
       <c r="R20" t="n">
-        <v>7076620</v>
+        <v>7076863</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025516</v>
+        <v>124025506</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3309,21 +3309,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471711</v>
+        <v>472001</v>
       </c>
       <c r="R21" t="n">
-        <v>7077040</v>
+        <v>7076620</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025510</v>
+        <v>124025505</v>
       </c>
       <c r="B22" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3416,16 +3416,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471995</v>
+        <v>471942</v>
       </c>
       <c r="R22" t="n">
-        <v>7076863</v>
+        <v>7076805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025505</v>
+        <v>124025516</v>
       </c>
       <c r="B23" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3523,21 +3523,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471942</v>
+        <v>471711</v>
       </c>
       <c r="R23" t="n">
-        <v>7076805</v>
+        <v>7077040</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123963577</v>
+        <v>123964523</v>
       </c>
       <c r="B2" t="n">
         <v>78788</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471727</v>
+        <v>471894</v>
       </c>
       <c r="R2" t="n">
-        <v>7077044</v>
+        <v>7076712</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964115</v>
+        <v>123963892</v>
       </c>
       <c r="B3" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471850</v>
+        <v>471865</v>
       </c>
       <c r="R3" t="n">
-        <v>7076819</v>
+        <v>7076927</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,22 +921,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123964523</v>
+        <v>123964386</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,37 +970,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471894</v>
+        <v>471865</v>
       </c>
       <c r="R4" t="n">
-        <v>7076712</v>
+        <v>7076746</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,22 +1063,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1091,7 +1096,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123964678</v>
+        <v>123963664</v>
       </c>
       <c r="B5" t="n">
         <v>78788</v>
@@ -1131,13 +1136,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471871</v>
+        <v>471738</v>
       </c>
       <c r="R5" t="n">
-        <v>7076764</v>
+        <v>7077025</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1166,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1176,12 +1181,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1233,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123964031</v>
+        <v>123964781</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,21 +1254,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1273,13 +1278,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471868</v>
+        <v>471855</v>
       </c>
       <c r="R6" t="n">
-        <v>7076872</v>
+        <v>7076803</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1308,7 +1313,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1318,12 +1323,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1342,22 +1347,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1375,10 +1380,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123963999</v>
+        <v>123963577</v>
       </c>
       <c r="B7" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1391,39 +1396,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471870</v>
+        <v>471727</v>
       </c>
       <c r="R7" t="n">
-        <v>7076894</v>
+        <v>7077044</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,22 +1484,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123963664</v>
+        <v>123964409</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1533,37 +1533,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471738</v>
+        <v>471878</v>
       </c>
       <c r="R8" t="n">
-        <v>7077025</v>
+        <v>7076764</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1592,7 +1597,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1602,12 +1607,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,22 +1626,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1659,7 +1659,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123963803</v>
+        <v>123964646</v>
       </c>
       <c r="B9" t="n">
         <v>79870</v>
@@ -1693,24 +1693,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471859</v>
+        <v>471902</v>
       </c>
       <c r="R9" t="n">
-        <v>7076971</v>
+        <v>7076746</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1739,7 +1734,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1749,7 +1744,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1778,12 +1773,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1801,7 +1796,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123963743</v>
+        <v>123964115</v>
       </c>
       <c r="B10" t="n">
         <v>79870</v>
@@ -1846,13 +1841,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471788</v>
+        <v>471850</v>
       </c>
       <c r="R10" t="n">
-        <v>7076975</v>
+        <v>7076819</v>
       </c>
       <c r="S10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1891,12 +1886,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1948,7 +1938,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123963518</v>
+        <v>123963999</v>
       </c>
       <c r="B11" t="n">
         <v>79870</v>
@@ -1993,13 +1983,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471708</v>
+        <v>471870</v>
       </c>
       <c r="R11" t="n">
-        <v>7077042</v>
+        <v>7076894</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2028,7 +2018,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2038,7 +2028,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2090,7 +2080,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123963841</v>
+        <v>123963803</v>
       </c>
       <c r="B12" t="n">
         <v>79870</v>
@@ -2135,13 +2125,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471864</v>
+        <v>471859</v>
       </c>
       <c r="R12" t="n">
-        <v>7076925</v>
+        <v>7076971</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2170,7 +2160,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2180,7 +2170,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2232,10 +2222,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123963892</v>
+        <v>123963841</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2248,34 +2238,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471865</v>
+        <v>471864</v>
       </c>
       <c r="R13" t="n">
-        <v>7076927</v>
+        <v>7076925</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2307,7 +2302,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2317,12 +2312,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2341,22 +2331,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2374,10 +2364,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123964409</v>
+        <v>123964678</v>
       </c>
       <c r="B14" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2390,42 +2380,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471878</v>
+        <v>471871</v>
       </c>
       <c r="R14" t="n">
         <v>7076764</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2454,7 +2439,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2464,7 +2449,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2483,22 +2473,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2516,10 +2506,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123964386</v>
+        <v>123964031</v>
       </c>
       <c r="B15" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2532,42 +2522,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471865</v>
+        <v>471868</v>
       </c>
       <c r="R15" t="n">
-        <v>7076746</v>
+        <v>7076872</v>
       </c>
       <c r="S15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2596,7 +2581,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2606,7 +2591,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2625,22 +2615,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2658,10 +2648,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123964781</v>
+        <v>123963743</v>
       </c>
       <c r="B16" t="n">
-        <v>79869</v>
+        <v>79870</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2674,37 +2664,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471855</v>
+        <v>471788</v>
       </c>
       <c r="R16" t="n">
-        <v>7076803</v>
+        <v>7076975</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2733,7 +2728,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2743,12 +2738,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2800,7 +2795,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123964646</v>
+        <v>123964621</v>
       </c>
       <c r="B17" t="n">
         <v>79870</v>
@@ -2834,19 +2829,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471902</v>
+        <v>471910</v>
       </c>
       <c r="R17" t="n">
-        <v>7076746</v>
+        <v>7076731</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2914,12 +2914,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123964621</v>
+        <v>123963518</v>
       </c>
       <c r="B18" t="n">
         <v>79870</v>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471910</v>
+        <v>471708</v>
       </c>
       <c r="R18" t="n">
-        <v>7076731</v>
+        <v>7077042</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025510</v>
+        <v>124025516</v>
       </c>
       <c r="B20" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,21 +3202,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471995</v>
+        <v>471711</v>
       </c>
       <c r="R20" t="n">
-        <v>7076863</v>
+        <v>7077040</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025506</v>
+        <v>124025510</v>
       </c>
       <c r="B21" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3309,16 +3309,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472001</v>
+        <v>471995</v>
       </c>
       <c r="R21" t="n">
-        <v>7076620</v>
+        <v>7076863</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3400,7 +3400,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025505</v>
+        <v>124025506</v>
       </c>
       <c r="B22" t="n">
         <v>57491</v>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471942</v>
+        <v>472001</v>
       </c>
       <c r="R22" t="n">
-        <v>7076805</v>
+        <v>7076620</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3507,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025516</v>
+        <v>124025505</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3523,21 +3523,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471711</v>
+        <v>471942</v>
       </c>
       <c r="R23" t="n">
-        <v>7077040</v>
+        <v>7076805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -1238,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123964781</v>
+        <v>123963577</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,21 +1254,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1278,13 +1278,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471855</v>
+        <v>471727</v>
       </c>
       <c r="R6" t="n">
-        <v>7076803</v>
+        <v>7077044</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1323,12 +1323,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,22 +1342,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1380,10 +1375,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123963577</v>
+        <v>123964781</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1396,21 +1391,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1420,13 +1415,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471727</v>
+        <v>471855</v>
       </c>
       <c r="R7" t="n">
-        <v>7077044</v>
+        <v>7076803</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1455,7 +1450,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1465,7 +1460,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,22 +1484,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025507</v>
+        <v>124025516</v>
       </c>
       <c r="B19" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472052</v>
+        <v>471711</v>
       </c>
       <c r="R19" t="n">
-        <v>7076789</v>
+        <v>7077040</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025516</v>
+        <v>124025507</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,21 +3202,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471711</v>
+        <v>472052</v>
       </c>
       <c r="R20" t="n">
-        <v>7077040</v>
+        <v>7076789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964523</v>
+        <v>123963803</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471894</v>
+        <v>471859</v>
       </c>
       <c r="R2" t="n">
-        <v>7076712</v>
+        <v>7076971</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123963892</v>
+        <v>123963518</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +833,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471865</v>
+        <v>471708</v>
       </c>
       <c r="R3" t="n">
-        <v>7076927</v>
+        <v>7077042</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,22 +926,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,7 +959,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123964386</v>
+        <v>123964781</v>
       </c>
       <c r="B4" t="n">
         <v>79869</v>
@@ -988,24 +993,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471865</v>
+        <v>471855</v>
       </c>
       <c r="R4" t="n">
-        <v>7076746</v>
+        <v>7076803</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1238,7 +1243,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123963577</v>
+        <v>123963892</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1278,13 +1283,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471727</v>
+        <v>471865</v>
       </c>
       <c r="R6" t="n">
-        <v>7077044</v>
+        <v>7076927</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1318,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1323,7 +1328,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1375,10 +1385,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123964781</v>
+        <v>123964523</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1391,21 +1401,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1415,13 +1425,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471855</v>
+        <v>471894</v>
       </c>
       <c r="R7" t="n">
-        <v>7076803</v>
+        <v>7076712</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1450,7 +1460,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1460,12 +1470,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1484,22 +1489,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1517,7 +1522,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123964409</v>
+        <v>123963743</v>
       </c>
       <c r="B8" t="n">
         <v>79870</v>
@@ -1562,13 +1567,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471878</v>
+        <v>471788</v>
       </c>
       <c r="R8" t="n">
-        <v>7076764</v>
+        <v>7076975</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,7 +1612,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1659,7 +1669,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123964646</v>
+        <v>123964115</v>
       </c>
       <c r="B9" t="n">
         <v>79870</v>
@@ -1693,19 +1703,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471902</v>
+        <v>471850</v>
       </c>
       <c r="R9" t="n">
-        <v>7076746</v>
+        <v>7076819</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1734,7 +1749,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1744,7 +1759,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1773,12 +1788,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1796,7 +1811,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123964115</v>
+        <v>123964621</v>
       </c>
       <c r="B10" t="n">
         <v>79870</v>
@@ -1841,10 +1856,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471850</v>
+        <v>471910</v>
       </c>
       <c r="R10" t="n">
-        <v>7076819</v>
+        <v>7076731</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1876,7 +1891,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1886,7 +1901,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1938,10 +1953,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123963999</v>
+        <v>123963577</v>
       </c>
       <c r="B11" t="n">
-        <v>79870</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1954,39 +1969,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471870</v>
+        <v>471727</v>
       </c>
       <c r="R11" t="n">
-        <v>7076894</v>
+        <v>7077044</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -2018,7 +2028,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2028,7 +2038,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2047,22 +2057,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2080,7 +2090,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123963803</v>
+        <v>123964646</v>
       </c>
       <c r="B12" t="n">
         <v>79870</v>
@@ -2114,24 +2124,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471859</v>
+        <v>471902</v>
       </c>
       <c r="R12" t="n">
-        <v>7076971</v>
+        <v>7076746</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2160,7 +2165,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2170,7 +2175,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2199,12 +2204,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2222,10 +2227,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123963841</v>
+        <v>123964386</v>
       </c>
       <c r="B13" t="n">
-        <v>79870</v>
+        <v>79869</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2238,21 +2243,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2267,13 +2272,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471864</v>
+        <v>471865</v>
       </c>
       <c r="R13" t="n">
-        <v>7076925</v>
+        <v>7076746</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2302,7 +2307,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2312,7 +2317,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2364,7 +2369,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123964678</v>
+        <v>123964031</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2404,13 +2409,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471871</v>
+        <v>471868</v>
       </c>
       <c r="R14" t="n">
-        <v>7076764</v>
+        <v>7076872</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2439,7 +2444,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2449,7 +2454,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2506,7 +2511,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123964031</v>
+        <v>123964678</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2546,13 +2551,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471868</v>
+        <v>471871</v>
       </c>
       <c r="R15" t="n">
-        <v>7076872</v>
+        <v>7076764</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2581,7 +2586,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2591,7 +2596,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2648,7 +2653,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123963743</v>
+        <v>123963841</v>
       </c>
       <c r="B16" t="n">
         <v>79870</v>
@@ -2693,13 +2698,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471788</v>
+        <v>471864</v>
       </c>
       <c r="R16" t="n">
-        <v>7076975</v>
+        <v>7076925</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2728,7 +2733,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2738,12 +2743,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2795,7 +2795,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123964621</v>
+        <v>123964409</v>
       </c>
       <c r="B17" t="n">
         <v>79870</v>
@@ -2840,13 +2840,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471910</v>
+        <v>471878</v>
       </c>
       <c r="R17" t="n">
-        <v>7076731</v>
+        <v>7076764</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2937,7 +2937,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123963518</v>
+        <v>123963999</v>
       </c>
       <c r="B18" t="n">
         <v>79870</v>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471708</v>
+        <v>471870</v>
       </c>
       <c r="R18" t="n">
-        <v>7077042</v>
+        <v>7076894</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3079,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025516</v>
+        <v>124025507</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,21 +3095,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471711</v>
+        <v>472052</v>
       </c>
       <c r="R19" t="n">
-        <v>7077040</v>
+        <v>7076789</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,7 +3186,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025507</v>
+        <v>124025506</v>
       </c>
       <c r="B20" t="n">
         <v>57491</v>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472052</v>
+        <v>472001</v>
       </c>
       <c r="R20" t="n">
-        <v>7076789</v>
+        <v>7076620</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025510</v>
+        <v>124025505</v>
       </c>
       <c r="B21" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3309,16 +3309,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471995</v>
+        <v>471942</v>
       </c>
       <c r="R21" t="n">
-        <v>7076863</v>
+        <v>7076805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025506</v>
+        <v>124025516</v>
       </c>
       <c r="B22" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472001</v>
+        <v>471711</v>
       </c>
       <c r="R22" t="n">
-        <v>7076620</v>
+        <v>7077040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025505</v>
+        <v>124025510</v>
       </c>
       <c r="B23" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471942</v>
+        <v>471995</v>
       </c>
       <c r="R23" t="n">
-        <v>7076805</v>
+        <v>7076863</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123963841</v>
+        <v>123964386</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471864</v>
+        <v>471865</v>
       </c>
       <c r="R2" t="n">
-        <v>7076925</v>
+        <v>7076746</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -817,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964646</v>
+        <v>123964523</v>
       </c>
       <c r="B3" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,21 +833,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471902</v>
+        <v>471894</v>
       </c>
       <c r="R3" t="n">
-        <v>7076746</v>
+        <v>7076712</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,22 +921,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123963743</v>
+        <v>123963664</v>
       </c>
       <c r="B4" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,42 +970,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471788</v>
+        <v>471738</v>
       </c>
       <c r="R4" t="n">
-        <v>7076975</v>
+        <v>7077025</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,22 +1063,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123963892</v>
+        <v>123963803</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,37 +1112,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471865</v>
+        <v>471859</v>
       </c>
       <c r="R5" t="n">
-        <v>7076927</v>
+        <v>7076971</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,12 +1186,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,22 +1205,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1243,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123964386</v>
+        <v>123963841</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,21 +1254,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1288,13 +1283,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471865</v>
+        <v>471864</v>
       </c>
       <c r="R6" t="n">
-        <v>7076746</v>
+        <v>7076925</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1323,7 +1318,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1333,7 +1328,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1385,7 +1380,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123963518</v>
+        <v>123964646</v>
       </c>
       <c r="B7" t="n">
         <v>79892</v>
@@ -1419,24 +1414,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471708</v>
+        <v>471902</v>
       </c>
       <c r="R7" t="n">
-        <v>7077042</v>
+        <v>7076746</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1465,7 +1455,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1475,7 +1465,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1504,12 +1494,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123963577</v>
+        <v>123964409</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1543,37 +1533,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471727</v>
+        <v>471878</v>
       </c>
       <c r="R8" t="n">
-        <v>7077044</v>
+        <v>7076764</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1612,7 +1607,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1631,22 +1626,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1664,7 +1659,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123963664</v>
+        <v>123964031</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1704,13 +1699,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471738</v>
+        <v>471868</v>
       </c>
       <c r="R9" t="n">
-        <v>7077025</v>
+        <v>7076872</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1739,7 +1734,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1749,12 +1744,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1806,10 +1801,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123963803</v>
+        <v>123963577</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1822,39 +1817,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471859</v>
+        <v>471727</v>
       </c>
       <c r="R10" t="n">
-        <v>7076971</v>
+        <v>7077044</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1886,7 +1876,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1896,7 +1886,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1915,22 +1905,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1948,10 +1938,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123964678</v>
+        <v>123963743</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1964,37 +1954,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471871</v>
+        <v>471788</v>
       </c>
       <c r="R11" t="n">
-        <v>7076764</v>
+        <v>7076975</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2023,7 +2018,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2033,12 +2028,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2057,22 +2052,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2090,10 +2085,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123964031</v>
+        <v>123963518</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2106,37 +2101,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471868</v>
+        <v>471708</v>
       </c>
       <c r="R12" t="n">
-        <v>7076872</v>
+        <v>7077042</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2175,12 +2175,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2199,22 +2194,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2232,7 +2227,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123964409</v>
+        <v>123964621</v>
       </c>
       <c r="B13" t="n">
         <v>79892</v>
@@ -2277,13 +2272,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471878</v>
+        <v>471910</v>
       </c>
       <c r="R13" t="n">
-        <v>7076764</v>
+        <v>7076731</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2312,7 +2307,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2322,7 +2317,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2374,10 +2369,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123964621</v>
+        <v>123964781</v>
       </c>
       <c r="B14" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2390,42 +2385,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471910</v>
+        <v>471855</v>
       </c>
       <c r="R14" t="n">
-        <v>7076731</v>
+        <v>7076803</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2454,7 +2444,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2464,7 +2454,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2658,10 +2653,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123964781</v>
+        <v>123964678</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2674,21 +2669,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2698,13 +2693,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471855</v>
+        <v>471871</v>
       </c>
       <c r="R16" t="n">
-        <v>7076803</v>
+        <v>7076764</v>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2733,7 +2728,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2743,12 +2738,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en grov gammal sälg.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2767,22 +2762,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2800,10 +2795,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123964523</v>
+        <v>123964115</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2816,37 +2811,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471894</v>
+        <v>471850</v>
       </c>
       <c r="R17" t="n">
-        <v>7076712</v>
+        <v>7076819</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2904,22 +2904,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123964115</v>
+        <v>123963892</v>
       </c>
       <c r="B18" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2953,42 +2953,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471850</v>
+        <v>471865</v>
       </c>
       <c r="R18" t="n">
-        <v>7076819</v>
+        <v>7076927</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3017,7 +3012,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3027,7 +3022,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3046,22 +3046,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025505</v>
+        <v>124025510</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,16 +3095,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471942</v>
+        <v>471995</v>
       </c>
       <c r="R19" t="n">
-        <v>7076805</v>
+        <v>7076863</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,7 +3186,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025506</v>
+        <v>124025507</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472001</v>
+        <v>472052</v>
       </c>
       <c r="R20" t="n">
-        <v>7076620</v>
+        <v>7076789</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025516</v>
+        <v>124025506</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3309,21 +3309,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471711</v>
+        <v>472001</v>
       </c>
       <c r="R21" t="n">
-        <v>7077040</v>
+        <v>7076620</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025507</v>
+        <v>124025516</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472052</v>
+        <v>471711</v>
       </c>
       <c r="R22" t="n">
-        <v>7076789</v>
+        <v>7077040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025510</v>
+        <v>124025505</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471995</v>
+        <v>471942</v>
       </c>
       <c r="R23" t="n">
-        <v>7076863</v>
+        <v>7076805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964386</v>
+        <v>123964523</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471865</v>
+        <v>471894</v>
       </c>
       <c r="R2" t="n">
-        <v>7076746</v>
+        <v>7076712</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964523</v>
+        <v>123963892</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -857,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471894</v>
+        <v>471865</v>
       </c>
       <c r="R3" t="n">
-        <v>7076712</v>
+        <v>7076927</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,7 +954,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123963664</v>
+        <v>123964678</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471738</v>
+        <v>471871</v>
       </c>
       <c r="R4" t="n">
-        <v>7077025</v>
+        <v>7076764</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1096,7 +1096,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123963803</v>
+        <v>123963743</v>
       </c>
       <c r="B5" t="n">
         <v>79892</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471859</v>
+        <v>471788</v>
       </c>
       <c r="R5" t="n">
-        <v>7076971</v>
+        <v>7076975</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,7 +1186,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1238,10 +1243,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123963841</v>
+        <v>123963664</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,39 +1259,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471864</v>
+        <v>471738</v>
       </c>
       <c r="R6" t="n">
-        <v>7076925</v>
+        <v>7077025</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1328,7 +1328,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,22 +1352,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1380,7 +1385,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123964646</v>
+        <v>123963518</v>
       </c>
       <c r="B7" t="n">
         <v>79892</v>
@@ -1414,19 +1419,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471902</v>
+        <v>471708</v>
       </c>
       <c r="R7" t="n">
-        <v>7076746</v>
+        <v>7077042</v>
       </c>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1455,7 +1465,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1465,7 +1475,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,12 +1504,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1517,7 +1527,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123964409</v>
+        <v>123964646</v>
       </c>
       <c r="B8" t="n">
         <v>79892</v>
@@ -1551,24 +1561,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471878</v>
+        <v>471902</v>
       </c>
       <c r="R8" t="n">
-        <v>7076764</v>
+        <v>7076746</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1602,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,7 +1612,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1636,12 +1641,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1659,10 +1664,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123964031</v>
+        <v>123964386</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1675,37 +1680,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471868</v>
+        <v>471865</v>
       </c>
       <c r="R9" t="n">
-        <v>7076872</v>
+        <v>7076746</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1734,7 +1744,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1744,12 +1754,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1768,22 +1773,22 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1801,10 +1806,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123963577</v>
+        <v>123964409</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1817,37 +1822,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471727</v>
+        <v>471878</v>
       </c>
       <c r="R10" t="n">
-        <v>7077044</v>
+        <v>7076764</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1876,7 +1886,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1886,7 +1896,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1905,22 +1915,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1938,7 +1948,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123963743</v>
+        <v>123964115</v>
       </c>
       <c r="B11" t="n">
         <v>79892</v>
@@ -1983,13 +1993,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471788</v>
+        <v>471850</v>
       </c>
       <c r="R11" t="n">
-        <v>7076975</v>
+        <v>7076819</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2018,7 +2028,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2028,12 +2038,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2085,7 +2090,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123963518</v>
+        <v>123963803</v>
       </c>
       <c r="B12" t="n">
         <v>79892</v>
@@ -2130,13 +2135,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471708</v>
+        <v>471859</v>
       </c>
       <c r="R12" t="n">
-        <v>7077042</v>
+        <v>7076971</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2175,7 +2180,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2227,10 +2232,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123964621</v>
+        <v>123964031</v>
       </c>
       <c r="B13" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2243,42 +2248,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471910</v>
+        <v>471868</v>
       </c>
       <c r="R13" t="n">
-        <v>7076731</v>
+        <v>7076872</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2317,7 +2317,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2336,22 +2341,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2511,7 +2516,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123963999</v>
+        <v>123963841</v>
       </c>
       <c r="B15" t="n">
         <v>79892</v>
@@ -2556,13 +2561,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471870</v>
+        <v>471864</v>
       </c>
       <c r="R15" t="n">
-        <v>7076894</v>
+        <v>7076925</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2591,7 +2596,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2601,7 +2606,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2653,10 +2658,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123964678</v>
+        <v>123963999</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2669,34 +2674,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471871</v>
+        <v>471870</v>
       </c>
       <c r="R16" t="n">
-        <v>7076764</v>
+        <v>7076894</v>
       </c>
       <c r="S16" t="n">
         <v>9</v>
@@ -2728,7 +2738,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2738,12 +2748,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2762,22 +2767,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2795,10 +2800,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123964115</v>
+        <v>123963577</v>
       </c>
       <c r="B17" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2811,39 +2816,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471850</v>
+        <v>471727</v>
       </c>
       <c r="R17" t="n">
-        <v>7076819</v>
+        <v>7077044</v>
       </c>
       <c r="S17" t="n">
         <v>9</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2904,22 +2904,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123963892</v>
+        <v>123964621</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2953,37 +2953,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471865</v>
+        <v>471910</v>
       </c>
       <c r="R18" t="n">
-        <v>7076927</v>
+        <v>7076731</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3012,7 +3017,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3022,12 +3027,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3046,22 +3046,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025510</v>
+        <v>124025506</v>
       </c>
       <c r="B19" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3095,16 +3095,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471995</v>
+        <v>472001</v>
       </c>
       <c r="R19" t="n">
-        <v>7076863</v>
+        <v>7076620</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3293,7 +3293,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025506</v>
+        <v>124025505</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472001</v>
+        <v>471942</v>
       </c>
       <c r="R21" t="n">
-        <v>7076620</v>
+        <v>7076805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3507,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025505</v>
+        <v>124025510</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471942</v>
+        <v>471995</v>
       </c>
       <c r="R23" t="n">
-        <v>7076805</v>
+        <v>7076863</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964523</v>
+        <v>123963892</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471894</v>
+        <v>471865</v>
       </c>
       <c r="R2" t="n">
-        <v>7076712</v>
+        <v>7076927</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123963892</v>
+        <v>123964409</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +833,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471865</v>
+        <v>471878</v>
       </c>
       <c r="R3" t="n">
-        <v>7076927</v>
+        <v>7076764</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,22 +926,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -954,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123964678</v>
+        <v>123963803</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -970,34 +975,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471871</v>
+        <v>471859</v>
       </c>
       <c r="R4" t="n">
-        <v>7076764</v>
+        <v>7076971</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1029,7 +1039,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,12 +1049,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,22 +1068,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,10 +1101,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123963743</v>
+        <v>123964386</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,21 +1117,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1141,13 +1146,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471788</v>
+        <v>471865</v>
       </c>
       <c r="R5" t="n">
-        <v>7076975</v>
+        <v>7076746</v>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1181,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,12 +1191,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1243,10 +1243,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123963664</v>
+        <v>123963999</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,37 +1259,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471738</v>
+        <v>471870</v>
       </c>
       <c r="R6" t="n">
-        <v>7077025</v>
+        <v>7076894</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1318,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1328,12 +1333,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:34</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,22 +1352,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123963518</v>
+        <v>123963577</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1401,42 +1401,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471708</v>
+        <v>471727</v>
       </c>
       <c r="R7" t="n">
-        <v>7077042</v>
+        <v>7077044</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1465,7 +1460,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1475,7 +1470,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1494,22 +1489,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1527,10 +1522,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123964646</v>
+        <v>123964678</v>
       </c>
       <c r="B8" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1543,21 +1538,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1567,13 +1562,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471902</v>
+        <v>471871</v>
       </c>
       <c r="R8" t="n">
-        <v>7076746</v>
+        <v>7076764</v>
       </c>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1602,7 +1597,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1612,7 +1607,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123964386</v>
+        <v>123964646</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1680,36 +1680,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471865</v>
+        <v>471902</v>
       </c>
       <c r="R9" t="n">
         <v>7076746</v>
@@ -1744,7 +1739,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1754,7 +1749,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1783,12 +1778,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1806,7 +1801,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123964409</v>
+        <v>123963518</v>
       </c>
       <c r="B10" t="n">
         <v>79892</v>
@@ -1851,13 +1846,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471878</v>
+        <v>471708</v>
       </c>
       <c r="R10" t="n">
-        <v>7076764</v>
+        <v>7077042</v>
       </c>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1886,7 +1881,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1896,7 +1891,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1948,7 +1943,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123964115</v>
+        <v>123963743</v>
       </c>
       <c r="B11" t="n">
         <v>79892</v>
@@ -1993,13 +1988,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471850</v>
+        <v>471788</v>
       </c>
       <c r="R11" t="n">
-        <v>7076819</v>
+        <v>7076975</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2028,7 +2023,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2038,7 +2033,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2090,7 +2090,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123963803</v>
+        <v>123964621</v>
       </c>
       <c r="B12" t="n">
         <v>79892</v>
@@ -2135,10 +2135,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471859</v>
+        <v>471910</v>
       </c>
       <c r="R12" t="n">
-        <v>7076971</v>
+        <v>7076731</v>
       </c>
       <c r="S12" t="n">
         <v>9</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123964031</v>
+        <v>123963664</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471868</v>
+        <v>471738</v>
       </c>
       <c r="R13" t="n">
-        <v>7076872</v>
+        <v>7077025</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2374,10 +2374,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123964781</v>
+        <v>123964115</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2390,37 +2390,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471855</v>
+        <v>471850</v>
       </c>
       <c r="R14" t="n">
-        <v>7076803</v>
+        <v>7076819</v>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2449,7 +2454,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2459,12 +2464,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123963841</v>
+        <v>123964031</v>
       </c>
       <c r="B15" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2532,42 +2532,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471864</v>
+        <v>471868</v>
       </c>
       <c r="R15" t="n">
-        <v>7076925</v>
+        <v>7076872</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2596,7 +2591,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2606,7 +2601,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2625,22 +2625,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123963999</v>
+        <v>123963841</v>
       </c>
       <c r="B16" t="n">
         <v>79892</v>
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471870</v>
+        <v>471864</v>
       </c>
       <c r="R16" t="n">
-        <v>7076894</v>
+        <v>7076925</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2800,10 +2800,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123963577</v>
+        <v>123964781</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2840,13 +2840,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471727</v>
+        <v>471855</v>
       </c>
       <c r="R17" t="n">
-        <v>7077044</v>
+        <v>7076803</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,7 +2885,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2904,22 +2909,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2937,10 +2942,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123964621</v>
+        <v>123964523</v>
       </c>
       <c r="B18" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2953,42 +2958,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471910</v>
+        <v>471894</v>
       </c>
       <c r="R18" t="n">
-        <v>7076731</v>
+        <v>7076712</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3046,22 +3046,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025506</v>
+        <v>124025507</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472001</v>
+        <v>472052</v>
       </c>
       <c r="R19" t="n">
-        <v>7076620</v>
+        <v>7076789</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,10 +3186,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025507</v>
+        <v>124025510</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472052</v>
+        <v>471995</v>
       </c>
       <c r="R20" t="n">
-        <v>7076789</v>
+        <v>7076863</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025505</v>
+        <v>124025516</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3309,21 +3309,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471942</v>
+        <v>471711</v>
       </c>
       <c r="R21" t="n">
-        <v>7076805</v>
+        <v>7077040</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025516</v>
+        <v>124025505</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471711</v>
+        <v>471942</v>
       </c>
       <c r="R22" t="n">
-        <v>7077040</v>
+        <v>7076805</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025510</v>
+        <v>124025506</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471995</v>
+        <v>472001</v>
       </c>
       <c r="R23" t="n">
-        <v>7076863</v>
+        <v>7076620</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123963892</v>
+        <v>123963803</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471865</v>
+        <v>471859</v>
       </c>
       <c r="R2" t="n">
-        <v>7076927</v>
+        <v>7076971</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +784,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +817,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964409</v>
+        <v>123964386</v>
       </c>
       <c r="B3" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,21 +833,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471878</v>
+        <v>471865</v>
       </c>
       <c r="R3" t="n">
-        <v>7076764</v>
+        <v>7076746</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -959,10 +959,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123963803</v>
+        <v>123963577</v>
       </c>
       <c r="B4" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,39 +975,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471859</v>
+        <v>471727</v>
       </c>
       <c r="R4" t="n">
-        <v>7076971</v>
+        <v>7077044</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1039,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1049,7 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,22 +1063,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1101,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123964386</v>
+        <v>123964523</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1117,42 +1112,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471865</v>
+        <v>471894</v>
       </c>
       <c r="R5" t="n">
-        <v>7076746</v>
+        <v>7076712</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1181,7 +1171,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1191,7 +1181,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1210,22 +1200,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1385,7 +1375,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123963577</v>
+        <v>123963892</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1425,13 +1415,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471727</v>
+        <v>471865</v>
       </c>
       <c r="R7" t="n">
-        <v>7077044</v>
+        <v>7076927</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1460,7 +1450,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1470,7 +1460,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1522,10 +1517,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123964678</v>
+        <v>123964409</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1538,37 +1533,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471871</v>
+        <v>471878</v>
       </c>
       <c r="R8" t="n">
         <v>7076764</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,12 +1607,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1631,22 +1626,22 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1664,7 +1659,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123964646</v>
+        <v>123963841</v>
       </c>
       <c r="B9" t="n">
         <v>79892</v>
@@ -1698,19 +1693,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471902</v>
+        <v>471864</v>
       </c>
       <c r="R9" t="n">
-        <v>7076746</v>
+        <v>7076925</v>
       </c>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1943,10 +1943,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123963743</v>
+        <v>123963664</v>
       </c>
       <c r="B11" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1959,42 +1959,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471788</v>
+        <v>471738</v>
       </c>
       <c r="R11" t="n">
-        <v>7076975</v>
+        <v>7077025</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2023,7 +2018,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2033,12 +2028,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2057,22 +2052,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2090,7 +2085,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123964621</v>
+        <v>123963743</v>
       </c>
       <c r="B12" t="n">
         <v>79892</v>
@@ -2135,13 +2130,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471910</v>
+        <v>471788</v>
       </c>
       <c r="R12" t="n">
-        <v>7076731</v>
+        <v>7076975</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2170,7 +2165,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2180,7 +2175,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123963664</v>
+        <v>123964031</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -2272,13 +2272,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471738</v>
+        <v>471868</v>
       </c>
       <c r="R13" t="n">
-        <v>7077025</v>
+        <v>7076872</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2317,12 +2317,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2374,7 +2374,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123964115</v>
+        <v>123964621</v>
       </c>
       <c r="B14" t="n">
         <v>79892</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471850</v>
+        <v>471910</v>
       </c>
       <c r="R14" t="n">
-        <v>7076819</v>
+        <v>7076731</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2516,7 +2516,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123964031</v>
+        <v>123964678</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471868</v>
+        <v>471871</v>
       </c>
       <c r="R15" t="n">
-        <v>7076872</v>
+        <v>7076764</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2658,7 +2658,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123963841</v>
+        <v>123964115</v>
       </c>
       <c r="B16" t="n">
         <v>79892</v>
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471864</v>
+        <v>471850</v>
       </c>
       <c r="R16" t="n">
-        <v>7076925</v>
+        <v>7076819</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2942,10 +2942,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123964523</v>
+        <v>123964646</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2958,21 +2958,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471894</v>
+        <v>471902</v>
       </c>
       <c r="R18" t="n">
-        <v>7076712</v>
+        <v>7076746</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3046,22 +3046,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123963803</v>
+        <v>123964523</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471859</v>
+        <v>471894</v>
       </c>
       <c r="R2" t="n">
-        <v>7076971</v>
+        <v>7076712</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -817,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964386</v>
+        <v>123963518</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,21 +828,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -862,13 +857,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471865</v>
+        <v>471708</v>
       </c>
       <c r="R3" t="n">
-        <v>7076746</v>
+        <v>7077042</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -897,7 +892,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -907,7 +902,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -959,10 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123963577</v>
+        <v>123964386</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,37 +970,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471727</v>
+        <v>471865</v>
       </c>
       <c r="R4" t="n">
-        <v>7077044</v>
+        <v>7076746</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123964523</v>
+        <v>123963803</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,37 +1112,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471894</v>
+        <v>471859</v>
       </c>
       <c r="R5" t="n">
-        <v>7076712</v>
+        <v>7076971</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1171,7 +1176,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1181,7 +1186,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,22 +1205,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1233,10 +1238,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123963999</v>
+        <v>123963892</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1249,42 +1254,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471870</v>
+        <v>471865</v>
       </c>
       <c r="R6" t="n">
-        <v>7076894</v>
+        <v>7076927</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1323,7 +1323,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1342,22 +1347,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1375,7 +1380,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123963892</v>
+        <v>123964031</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1415,13 +1420,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471865</v>
+        <v>471868</v>
       </c>
       <c r="R7" t="n">
-        <v>7076927</v>
+        <v>7076872</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1450,7 +1455,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1460,12 +1465,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hyfsat rikligt.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1517,10 +1522,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123964409</v>
+        <v>123964781</v>
       </c>
       <c r="B8" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1533,42 +1538,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471878</v>
+        <v>471855</v>
       </c>
       <c r="R8" t="n">
-        <v>7076764</v>
+        <v>7076803</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,7 +1607,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1659,7 +1664,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123963841</v>
+        <v>123964621</v>
       </c>
       <c r="B9" t="n">
         <v>79892</v>
@@ -1704,13 +1709,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471864</v>
+        <v>471910</v>
       </c>
       <c r="R9" t="n">
-        <v>7076925</v>
+        <v>7076731</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1739,7 +1744,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1749,7 +1754,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1801,7 +1806,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123963518</v>
+        <v>123963999</v>
       </c>
       <c r="B10" t="n">
         <v>79892</v>
@@ -1846,13 +1851,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471708</v>
+        <v>471870</v>
       </c>
       <c r="R10" t="n">
-        <v>7077042</v>
+        <v>7076894</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1881,7 +1886,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1891,7 +1896,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1943,7 +1948,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123963664</v>
+        <v>123964678</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1983,13 +1988,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471738</v>
+        <v>471871</v>
       </c>
       <c r="R11" t="n">
-        <v>7077025</v>
+        <v>7076764</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2018,7 +2023,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2028,12 +2033,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2085,7 +2090,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123963743</v>
+        <v>123963841</v>
       </c>
       <c r="B12" t="n">
         <v>79892</v>
@@ -2130,13 +2135,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471788</v>
+        <v>471864</v>
       </c>
       <c r="R12" t="n">
-        <v>7076975</v>
+        <v>7076925</v>
       </c>
       <c r="S12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2165,7 +2170,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2175,12 +2180,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123964031</v>
+        <v>123964409</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2248,37 +2248,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471868</v>
+        <v>471878</v>
       </c>
       <c r="R13" t="n">
-        <v>7076872</v>
+        <v>7076764</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2307,7 +2312,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2317,12 +2322,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2341,22 +2341,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123964621</v>
+        <v>123963664</v>
       </c>
       <c r="B14" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2390,42 +2390,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471910</v>
+        <v>471738</v>
       </c>
       <c r="R14" t="n">
-        <v>7076731</v>
+        <v>7077025</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2454,7 +2449,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2464,7 +2459,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2483,22 +2483,22 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123964678</v>
+        <v>123964115</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2532,34 +2532,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471871</v>
+        <v>471850</v>
       </c>
       <c r="R15" t="n">
-        <v>7076764</v>
+        <v>7076819</v>
       </c>
       <c r="S15" t="n">
         <v>9</v>
@@ -2591,7 +2596,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2601,12 +2606,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2625,22 +2625,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123964115</v>
+        <v>123963743</v>
       </c>
       <c r="B16" t="n">
         <v>79892</v>
@@ -2703,13 +2703,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471850</v>
+        <v>471788</v>
       </c>
       <c r="R16" t="n">
-        <v>7076819</v>
+        <v>7076975</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2748,7 +2748,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2800,10 +2805,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123964781</v>
+        <v>123963577</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2816,21 +2821,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2840,13 +2845,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471855</v>
+        <v>471727</v>
       </c>
       <c r="R17" t="n">
-        <v>7076803</v>
+        <v>7077044</v>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2875,7 +2880,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2885,12 +2890,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3186,10 +3186,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025510</v>
+        <v>124025505</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471995</v>
+        <v>471942</v>
       </c>
       <c r="R20" t="n">
-        <v>7076863</v>
+        <v>7076805</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,10 +3293,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025516</v>
+        <v>124025506</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3309,21 +3309,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471711</v>
+        <v>472001</v>
       </c>
       <c r="R21" t="n">
-        <v>7077040</v>
+        <v>7076620</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025505</v>
+        <v>124025510</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3416,16 +3416,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471942</v>
+        <v>471995</v>
       </c>
       <c r="R22" t="n">
-        <v>7076805</v>
+        <v>7076863</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025506</v>
+        <v>124025516</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3523,21 +3523,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472001</v>
+        <v>471711</v>
       </c>
       <c r="R23" t="n">
-        <v>7076620</v>
+        <v>7077040</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -3079,7 +3079,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025507</v>
+        <v>124025505</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -3119,10 +3119,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472052</v>
+        <v>471942</v>
       </c>
       <c r="R19" t="n">
-        <v>7076789</v>
+        <v>7076805</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3186,7 +3186,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025505</v>
+        <v>124025506</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471942</v>
+        <v>472001</v>
       </c>
       <c r="R20" t="n">
-        <v>7076805</v>
+        <v>7076620</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025506</v>
+        <v>124025507</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472001</v>
+        <v>472052</v>
       </c>
       <c r="R21" t="n">
-        <v>7076620</v>
+        <v>7076789</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3400,10 +3400,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025510</v>
+        <v>124025516</v>
       </c>
       <c r="B22" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471995</v>
+        <v>471711</v>
       </c>
       <c r="R22" t="n">
-        <v>7076863</v>
+        <v>7077040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3507,10 +3507,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025516</v>
+        <v>124025510</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3523,21 +3523,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3547,10 +3547,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471711</v>
+        <v>471995</v>
       </c>
       <c r="R23" t="n">
-        <v>7077040</v>
+        <v>7076863</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964523</v>
+        <v>123963518</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471894</v>
+        <v>471708</v>
       </c>
       <c r="R2" t="n">
-        <v>7076712</v>
+        <v>7077042</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,15 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123963518</v>
+        <v>123963743</v>
       </c>
       <c r="B3" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -857,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471708</v>
+        <v>471788</v>
       </c>
       <c r="R3" t="n">
-        <v>7077042</v>
+        <v>7076975</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +897,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en gammal grov flerstammig sälg.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -954,15 +954,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123964386</v>
+        <v>123963803</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,21 +965,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -999,13 +994,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471865</v>
+        <v>471859</v>
       </c>
       <c r="R4" t="n">
-        <v>7076746</v>
+        <v>7076971</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1096,15 +1091,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123963803</v>
+        <v>123963841</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,13 +1131,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471859</v>
+        <v>471864</v>
       </c>
       <c r="R5" t="n">
-        <v>7076971</v>
+        <v>7076925</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1176,7 +1166,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1186,7 +1176,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1238,15 +1228,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123963892</v>
+        <v>123963999</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1254,37 +1239,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471865</v>
+        <v>471870</v>
       </c>
       <c r="R6" t="n">
-        <v>7076927</v>
+        <v>7076894</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1313,7 +1303,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1323,12 +1313,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hyfsat rikligt.</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,22 +1332,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1380,15 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123964031</v>
+        <v>123964115</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1396,37 +1376,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471868</v>
+        <v>471850</v>
       </c>
       <c r="R7" t="n">
-        <v>7076872</v>
+        <v>7076819</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1455,7 +1440,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1465,12 +1450,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1489,22 +1469,22 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1522,15 +1502,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123964781</v>
+        <v>123964409</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1538,37 +1513,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471855</v>
+        <v>471878</v>
       </c>
       <c r="R8" t="n">
-        <v>7076803</v>
+        <v>7076764</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1577,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1607,12 +1587,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg.</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1667,12 +1642,7 @@
         <v>123964621</v>
       </c>
       <c r="B9" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1806,15 +1776,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123963999</v>
+        <v>123964646</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1840,24 +1805,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471870</v>
+        <v>471902</v>
       </c>
       <c r="R10" t="n">
-        <v>7076894</v>
+        <v>7076746</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1886,7 +1846,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1896,7 +1856,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1925,12 +1885,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1948,19 +1908,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123964678</v>
+        <v>123963577</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1988,10 +1943,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471871</v>
+        <v>471727</v>
       </c>
       <c r="R11" t="n">
-        <v>7076764</v>
+        <v>7077044</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -2023,7 +1978,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -2033,12 +1988,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2090,55 +2040,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123963841</v>
+        <v>123963664</v>
       </c>
       <c r="B12" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471864</v>
+        <v>471738</v>
       </c>
       <c r="R12" t="n">
-        <v>7076925</v>
+        <v>7077025</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2170,7 +2110,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2180,7 +2120,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2199,22 +2144,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2232,58 +2177,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123964409</v>
+        <v>123963892</v>
       </c>
       <c r="B13" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471878</v>
+        <v>471865</v>
       </c>
       <c r="R13" t="n">
-        <v>7076764</v>
+        <v>7076927</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2312,7 +2247,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2322,7 +2257,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hyfsat rikligt.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2341,22 +2281,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2374,19 +2314,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123963664</v>
+        <v>123964031</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2414,13 +2349,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471738</v>
+        <v>471868</v>
       </c>
       <c r="R14" t="n">
-        <v>7077025</v>
+        <v>7076872</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2449,7 +2384,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2459,12 +2394,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2516,58 +2451,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123964115</v>
+        <v>123964523</v>
       </c>
       <c r="B15" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471850</v>
+        <v>471894</v>
       </c>
       <c r="R15" t="n">
-        <v>7076819</v>
+        <v>7076712</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2596,7 +2521,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2606,7 +2531,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2625,22 +2550,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2658,58 +2583,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123963743</v>
+        <v>123964678</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471788</v>
+        <v>471871</v>
       </c>
       <c r="R16" t="n">
-        <v>7076975</v>
+        <v>7076764</v>
       </c>
       <c r="S16" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2738,7 +2653,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2748,12 +2663,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en gammal grov flerstammig sälg.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2772,22 +2687,22 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2805,19 +2720,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123963577</v>
+        <v>124025516</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2841,17 +2751,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
+          <t>Norra Skärvången NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471727</v>
+        <v>471711</v>
       </c>
       <c r="R17" t="n">
-        <v>7077044</v>
+        <v>7077040</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2878,19 +2788,14 @@
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:31</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:31</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2901,56 +2806,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123964646</v>
+        <v>123964386</v>
       </c>
       <c r="B18" t="n">
-        <v>79892</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2958,31 +2833,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471902</v>
+        <v>471865</v>
       </c>
       <c r="R18" t="n">
         <v>7076746</v>
@@ -3017,7 +2897,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -3027,7 +2907,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3056,12 +2936,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3079,15 +2959,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124025505</v>
+        <v>123964781</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3095,37 +2970,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Norra Skärvången NÖ, Jmt</t>
+          <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471942</v>
+        <v>471855</v>
       </c>
       <c r="R19" t="n">
-        <v>7076805</v>
+        <v>7076803</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3152,14 +3027,24 @@
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På en grov gammal sälg.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3170,48 +3055,68 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124025506</v>
+        <v>124025510</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3226,10 +3131,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472001</v>
+        <v>471995</v>
       </c>
       <c r="R20" t="n">
-        <v>7076620</v>
+        <v>7076863</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3266,7 +3171,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack färska</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3293,15 +3198,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124025507</v>
+        <v>124025505</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3333,10 +3233,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472052</v>
+        <v>471942</v>
       </c>
       <c r="R21" t="n">
-        <v>7076789</v>
+        <v>7076805</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3373,7 +3273,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3400,15 +3300,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124025516</v>
+        <v>124025506</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3416,21 +3311,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3440,10 +3335,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>471711</v>
+        <v>472001</v>
       </c>
       <c r="R22" t="n">
-        <v>7077040</v>
+        <v>7076620</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3480,7 +3375,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3507,15 +3402,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124025510</v>
+        <v>124025507</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,16 +3413,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3547,10 +3437,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>471995</v>
+        <v>472052</v>
       </c>
       <c r="R23" t="n">
-        <v>7076863</v>
+        <v>7076789</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3587,7 +3477,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Hack färska</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 53815-2024 artfynd.xlsx
+++ b/artfynd/A 53815-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -809,6 +814,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123963518</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -951,6 +961,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123963743</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1088,6 +1103,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123963803</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1225,6 +1245,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123963841</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1362,6 +1387,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123963999</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1499,6 +1529,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964115</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1636,6 +1671,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964409</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1773,6 +1813,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964621</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1905,6 +1950,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964646</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2037,6 +2087,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123963577</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2174,6 +2229,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123963664</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2311,6 +2371,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123963892</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2448,6 +2513,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964031</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2580,6 +2650,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964523</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2717,6 +2792,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964678</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2819,6 +2899,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025516</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2956,6 +3041,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964386</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3093,6 +3183,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123964781</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3195,6 +3290,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025510</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3297,6 +3397,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025505</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3399,6 +3504,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025506</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3501,8 +3611,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025507</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>